--- a/Другое/работа/3. ТПУ 2 этап/_РАСЧЕТ.xlsx
+++ b/Другое/работа/3. ТПУ 2 этап/_РАСЧЕТ.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="63">
   <si>
     <t>Показатель</t>
   </si>
@@ -36,127 +36,34 @@
     <t>Значение</t>
   </si>
   <si>
-    <t>Стоимость рабочей документации 1 этап по ГК</t>
-  </si>
-  <si>
-    <t>ССРСС</t>
-  </si>
-  <si>
-    <t>Смета контракта</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Пересчет </t>
-  </si>
-  <si>
-    <t>Смета № 7 - Переустройство сетей связи</t>
-  </si>
-  <si>
-    <t>Смета № 8 - Переустройство линий электроснабжения</t>
-  </si>
-  <si>
-    <t>Смета № 9 - Переустрйство сетей газоснабжения</t>
-  </si>
-  <si>
-    <t>Стоимость рабочей документации 1 этап по ССРСС</t>
-  </si>
-  <si>
-    <t>1 этап</t>
-  </si>
-  <si>
-    <t>СМР + Рабочка</t>
-  </si>
-  <si>
-    <t>Том 1</t>
-  </si>
-  <si>
-    <t>Стоимость рабочей документации по сметным расчетам</t>
-  </si>
-  <si>
-    <t>Рабочая документация</t>
-  </si>
-  <si>
-    <t>С дефлятором</t>
+    <t>Стоимость РД 2 этап по ССРСС</t>
+  </si>
+  <si>
+    <t>Дефлятор (по Пересчету цены ГК)</t>
+  </si>
+  <si>
+    <t>Понижающий под лимиты (по Пересчету цены ГК)</t>
+  </si>
+  <si>
+    <t>Стоимость РД 2 этап по ГК</t>
   </si>
   <si>
     <t>Том 2</t>
   </si>
   <si>
-    <t>Дефлятор (по Пересчету цены ГК)</t>
-  </si>
-  <si>
-    <t>КЭФ Дефлятор</t>
+    <t>Том 3</t>
+  </si>
+  <si>
+    <t>Том 4</t>
   </si>
   <si>
     <t>Том 5</t>
   </si>
   <si>
-    <t>Всего</t>
-  </si>
-  <si>
-    <t>Понижающий (по Пересчету цены ГК)</t>
-  </si>
-  <si>
-    <t>Кэф пересчета</t>
-  </si>
-  <si>
-    <t>кэф текущих цен</t>
-  </si>
-  <si>
-    <t>Общий кэф (по пересчету цены ГК)</t>
-  </si>
-  <si>
-    <t>Стоимость всего (без ПИР)</t>
-  </si>
-  <si>
     <t>Том 6</t>
   </si>
   <si>
-    <t>в текущих ценах (кэф 5,42)</t>
-  </si>
-  <si>
-    <t>в текущих ценах</t>
-  </si>
-  <si>
-    <t>Общий кэф (ГК на стоимость по ССРСС)</t>
-  </si>
-  <si>
-    <t>С учетом понижающего</t>
-  </si>
-  <si>
-    <t>Том 3</t>
-  </si>
-  <si>
-    <t>в том числе стадия "Р"</t>
-  </si>
-  <si>
-    <t>КЭФ понижающий</t>
-  </si>
-  <si>
-    <t>с кэф пересчета</t>
-  </si>
-  <si>
-    <t>Итоговый КЭФ</t>
-  </si>
-  <si>
-    <t>Стоимость РД 2 этап по ГК</t>
-  </si>
-  <si>
-    <t>Стоимость РД 2 этап по ССРСС</t>
-  </si>
-  <si>
-    <t>Том 4</t>
-  </si>
-  <si>
     <t>Том 7</t>
-  </si>
-  <si>
-    <t>в текущих ценах (кэф = 5,42)</t>
-  </si>
-  <si>
-    <t>j</t>
-  </si>
-  <si>
-    <t>общий кэф</t>
   </si>
   <si>
     <t>ИТОГО</t>
@@ -378,16 +285,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="9">
+  <numFmts count="8">
     <numFmt numFmtId="176" formatCode="_-* #\.##0.00_-;\-* #\.##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-* #\.##0.00\ &quot;₽&quot;_-;\-* #\.##0.00\ &quot;₽&quot;_-;_-* \-??\ &quot;₽&quot;_-;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-* #\.##0_-;\-* #\.##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="179" formatCode="_-* #\.##0\ &quot;₽&quot;_-;\-* #\.##0\ &quot;₽&quot;_-;_-* \-\ &quot;₽&quot;_-;_-@_-"/>
     <numFmt numFmtId="180" formatCode="0.00000000000000"/>
     <numFmt numFmtId="181" formatCode="#\ ##0.00\ &quot;₽&quot;"/>
-    <numFmt numFmtId="182" formatCode="#\ ##0.00000000000000\ &quot;₽&quot;"/>
-    <numFmt numFmtId="183" formatCode="#\ ##0.000000000000000\ &quot;₽&quot;"/>
-    <numFmt numFmtId="184" formatCode="0.000000000000000"/>
+    <numFmt numFmtId="182" formatCode="0.000000000000000_ "/>
+    <numFmt numFmtId="183" formatCode="0.00_ "/>
   </numFmts>
   <fonts count="32">
     <font>
@@ -627,7 +533,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="40">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -781,12 +687,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1210,47 +1110,47 @@
     <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1339,29 +1239,21 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="181" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="183" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="184" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="180" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="181" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="181" fontId="9" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="180" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="181" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
@@ -1713,7 +1605,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B3:AH53"/>
+  <dimension ref="B3:AD41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="57" customWidth="1"/>
@@ -1738,7 +1630,7 @@
     <col min="33" max="33" width="19.858407079646" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:34">
+    <row r="3" spans="2:30">
       <c r="B3" s="30" t="s">
         <v>0</v>
       </c>
@@ -1746,716 +1638,227 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:34">
+    <row r="4" spans="2:30">
       <c r="B4" s="31" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="32">
-        <v>3301168</v>
-      </c>
-      <c r="J4" s="33" t="s">
-        <v>3</v>
-      </c>
-      <c r="K4" s="33"/>
-      <c r="N4" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="O4" s="33"/>
-      <c r="R4" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="S4" s="33"/>
-      <c r="W4" s="33" t="s">
-        <v>6</v>
-      </c>
-      <c r="X4" s="33"/>
-      <c r="AA4" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="AB4" s="33"/>
-      <c r="AC4" s="33"/>
-      <c r="AE4" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF4" s="33"/>
-      <c r="AG4" s="33"/>
-    </row>
-    <row r="5" spans="2:34">
-      <c r="B5" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="32">
-        <f>3205790</f>
-        <v>3205790</v>
-      </c>
-      <c r="D5" s="34"/>
-      <c r="J5" t="s">
-        <v>10</v>
-      </c>
-      <c r="N5" t="s">
-        <v>10</v>
-      </c>
-      <c r="R5" t="s">
-        <v>11</v>
-      </c>
-      <c r="S5" s="34">
-        <v>88421721.5</v>
-      </c>
-      <c r="W5" s="35">
-        <v>1</v>
-      </c>
-      <c r="X5" s="34">
-        <f>(2000+148*164)*1.05</f>
-        <v>27585.6</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>12</v>
-      </c>
-      <c r="AA5">
-        <v>1</v>
-      </c>
-      <c r="AB5" s="34">
-        <f>8265+620*41</f>
-        <v>33685</v>
-      </c>
-      <c r="AE5" s="35">
-        <v>1</v>
-      </c>
-      <c r="AF5" s="34">
-        <f>5221+137561*0.25</f>
-        <v>39611.25</v>
-      </c>
-    </row>
-    <row r="6" spans="2:34">
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="34">
-        <f>X26+AF10+AB10</f>
-        <v>3205790.2136</v>
-      </c>
-      <c r="D6" s="34"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="37"/>
-      <c r="J6" t="s">
-        <v>14</v>
-      </c>
-      <c r="K6" s="34">
-        <v>3205790</v>
-      </c>
-      <c r="N6" t="s">
-        <v>14</v>
-      </c>
-      <c r="O6" s="34">
-        <v>3301186</v>
-      </c>
-      <c r="R6" t="s">
-        <v>15</v>
-      </c>
-      <c r="S6" s="34">
-        <v>106565292.86</v>
-      </c>
-      <c r="W6" s="35">
-        <v>2</v>
-      </c>
-      <c r="X6" s="34">
-        <f>14450*1.05</f>
-        <v>15172.5</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA6">
-        <v>2</v>
-      </c>
-      <c r="AB6" s="34">
-        <f>9090*5</f>
-        <v>45450</v>
-      </c>
-      <c r="AE6" s="35">
-        <v>2</v>
-      </c>
-      <c r="AF6" s="34">
-        <f>5221+137561*0.13</f>
-        <v>23103.93</v>
-      </c>
-    </row>
-    <row r="7" spans="2:34">
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="38">
-        <f>S7</f>
-        <v>1.20519360008163</v>
-      </c>
-      <c r="R7" t="s">
-        <v>18</v>
-      </c>
-      <c r="S7" s="38">
-        <f>S6/S5</f>
-        <v>1.20519360008163</v>
-      </c>
-      <c r="W7" s="35">
-        <v>3</v>
-      </c>
-      <c r="X7" s="34">
-        <f>(750+137*157)*1.05</f>
-        <v>23371.95</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>19</v>
-      </c>
-      <c r="AA7">
-        <v>3</v>
-      </c>
-      <c r="AB7" s="34">
-        <v>2132</v>
-      </c>
-      <c r="AE7" t="s">
-        <v>20</v>
-      </c>
-      <c r="AF7" s="34">
-        <f>SUM(AF5:AF6)</f>
-        <v>62715.18</v>
-      </c>
-      <c r="AG7" s="34"/>
-    </row>
-    <row r="8" spans="2:34">
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="39">
-        <f>S11</f>
-        <v>0.854428678158152</v>
-      </c>
-      <c r="N8" s="40" t="s">
-        <v>22</v>
-      </c>
-      <c r="O8" s="40">
-        <f>O6/K6</f>
-        <v>1.02975740769046</v>
-      </c>
-      <c r="W8" s="35">
-        <v>4</v>
-      </c>
-      <c r="X8" s="34">
-        <f>15850*1.05</f>
-        <v>16642.5</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>19</v>
-      </c>
-      <c r="AA8" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB8" s="34">
-        <f>SUM(AB5:AB7)</f>
-        <v>81267</v>
-      </c>
-      <c r="AE8" t="s">
-        <v>23</v>
-      </c>
-      <c r="AF8" s="41">
-        <f>339.92/62.72</f>
-        <v>5.41964285714286</v>
-      </c>
-    </row>
-    <row r="9" spans="2:34">
-      <c r="B9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="38">
-        <f>C7*C8</f>
-        <v>1.02975197464241</v>
-      </c>
-      <c r="R9" t="s">
-        <v>25</v>
-      </c>
-      <c r="S9" s="34">
-        <v>6949970491.16</v>
-      </c>
-      <c r="W9" s="35">
-        <v>5</v>
-      </c>
-      <c r="X9" s="34">
-        <f>15850*1.1*1.05</f>
-        <v>18306.75</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA9" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB9" s="34">
-        <f>ROUND(AB8*5.42,2)</f>
-        <v>440467.14</v>
-      </c>
-      <c r="AE9" t="s">
-        <v>28</v>
-      </c>
-      <c r="AF9" s="34">
-        <f>ROUND(AF7*AF8,2)</f>
-        <v>339893.88</v>
-      </c>
-    </row>
-    <row r="10" spans="2:34">
-      <c r="B10" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" s="42">
-        <f>C4/C6</f>
-        <v>1.02975172423803</v>
-      </c>
-      <c r="R10" t="s">
-        <v>30</v>
-      </c>
-      <c r="S10" s="34">
-        <v>5938254100</v>
-      </c>
-      <c r="W10" s="35">
-        <v>6</v>
-      </c>
-      <c r="X10" s="34">
-        <f>15850*1.05</f>
-        <v>16642.5</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>31</v>
-      </c>
-      <c r="AA10" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB10" s="44">
-        <f>AB9*0.6</f>
-        <v>264280.284</v>
-      </c>
-      <c r="AE10" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="AF10" s="44">
-        <f>ROUND(AF9*0.6,2)</f>
-        <v>203936.33</v>
-      </c>
-    </row>
-    <row r="11" spans="2:34">
-      <c r="R11" t="s">
-        <v>33</v>
-      </c>
-      <c r="S11" s="39">
-        <f>S10/S9</f>
-        <v>0.854428678158152</v>
-      </c>
-      <c r="W11" s="35">
-        <v>7</v>
-      </c>
-      <c r="X11" s="34">
-        <f>(31000*1.05*1.2)+(31000*1.05*1.2*0.35)*2</f>
-        <v>66402</v>
-      </c>
-      <c r="Y11" t="s">
-        <v>12</v>
-      </c>
-      <c r="AA11" s="45" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB11" s="46">
-        <f>ROUND(AB10*C10,2)</f>
-        <v>272143.08</v>
-      </c>
-      <c r="AC11">
-        <v>272143</v>
-      </c>
-      <c r="AD11" s="34">
-        <f>AB11-AC11</f>
-        <v>0.0800000000162981</v>
-      </c>
-      <c r="AE11" s="45" t="s">
-        <v>34</v>
-      </c>
-      <c r="AF11" s="46">
-        <f>ROUND(AF10*C10,2)</f>
-        <v>210003.79</v>
-      </c>
-      <c r="AG11">
-        <v>210017</v>
-      </c>
-      <c r="AH11" s="34">
-        <f>AF11-AG11</f>
-        <v>-13.2099999999919</v>
-      </c>
-    </row>
-    <row r="12" spans="2:34">
-      <c r="R12" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="S12" s="42">
-        <f>S7*S11</f>
-        <v>1.02975197464241</v>
-      </c>
-      <c r="W12" s="35">
-        <v>8</v>
-      </c>
-      <c r="X12" s="34">
-        <f>(31000*1.05*1.2*1.2)*3</f>
-        <v>140616</v>
-      </c>
-      <c r="Y12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="2:34">
-      <c r="W13" s="35">
-        <v>9</v>
-      </c>
-      <c r="X13" s="34">
-        <f>(31000*1.05*1.2)</f>
-        <v>39060</v>
-      </c>
-      <c r="Y13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="2:34">
-      <c r="W14" s="35">
-        <v>10</v>
-      </c>
-      <c r="X14" s="34">
-        <f>(31000*1.05*1.2)+(31000*1.05*1.2*0.35)*2</f>
-        <v>66402</v>
-      </c>
-      <c r="Y14" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" spans="2:34">
-      <c r="B15" t="s">
-        <v>36</v>
-      </c>
-      <c r="C15" s="32">
-        <v>105908590.98</v>
-      </c>
-      <c r="W15" s="35">
-        <v>11</v>
-      </c>
-      <c r="X15" s="34">
-        <f>(33000*1.05)*2</f>
-        <v>69300</v>
-      </c>
-      <c r="Y15" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="2:34">
-      <c r="B16" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" s="32">
         <f>105864.73*1000</f>
         <v>105864730</v>
       </c>
-      <c r="W16" s="35">
+      <c r="W4" s="33"/>
+      <c r="X4" s="34"/>
+    </row>
+    <row r="5" spans="2:30">
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>1.1708576</v>
+      </c>
+      <c r="W5" s="33"/>
+      <c r="X5" s="34"/>
+    </row>
+    <row r="6" spans="2:30">
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="35">
+        <f>0.854428678158163</f>
+        <v>0.854428678158163</v>
+      </c>
+      <c r="W6" s="33"/>
+      <c r="X6" s="34"/>
+    </row>
+    <row r="7" spans="2:30">
+      <c r="C7" s="36">
+        <f>ROUND(C4*C5*C6,2)</f>
+        <v>105908590.97</v>
+      </c>
+      <c r="W7" s="33"/>
+      <c r="X7" s="34"/>
+    </row>
+    <row r="8" spans="2:30">
+      <c r="B8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="32">
+        <v>105908590.98</v>
+      </c>
+      <c r="W8" s="33"/>
+      <c r="X8" s="34"/>
+      <c r="Y8"/>
+      <c r="AB8" s="34"/>
+      <c r="AC8" s="34"/>
+      <c r="AD8" s="34"/>
+    </row>
+    <row r="9" spans="2:30">
+      <c r="W9" s="33"/>
+      <c r="X9" s="34"/>
+    </row>
+    <row r="10" spans="2:30">
+      <c r="W10" s="33"/>
+      <c r="X10" s="34"/>
+    </row>
+    <row r="11" spans="2:30">
+      <c r="W11" s="33"/>
+      <c r="X11" s="34"/>
+    </row>
+    <row r="12" spans="2:30">
+      <c r="W12" s="33"/>
+      <c r="X12" s="34"/>
+    </row>
+    <row r="13" spans="2:30">
+      <c r="W13" s="37"/>
+      <c r="X13" s="34"/>
+    </row>
+    <row r="14" spans="2:30">
+      <c r="W14" s="38"/>
+      <c r="X14" s="39"/>
+    </row>
+    <row r="15" spans="2:30">
+      <c r="W15" s="40"/>
+      <c r="X15" s="41"/>
+    </row>
+    <row r="16" spans="2:30">
+      <c r="W16" s="31"/>
+      <c r="X16" s="32"/>
+    </row>
+    <row r="17" spans="23:24">
+      <c r="W17" s="31"/>
+      <c r="X17" s="42"/>
+    </row>
+    <row r="19" spans="23:24">
+      <c r="W19" s="43"/>
+      <c r="X19" s="44"/>
+    </row>
+    <row r="20" spans="23:24">
+      <c r="W20" s="45"/>
+      <c r="X20" s="46">
+        <f>ROUND(X19*X17,2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="23:24">
+      <c r="W22" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="X22" s="44" t="e">
+        <f>SUM(#REF!,#REF!)</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="23" spans="23:24">
+      <c r="W23" s="45"/>
+      <c r="X23" s="46" t="e">
+        <f>ROUND(X22*X17,2)</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="25" spans="23:24">
+      <c r="W25" s="43" t="s">
+        <v>7</v>
+      </c>
+      <c r="X25" s="44" t="e">
+        <f>SUM(#REF!,X7,X8)</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="23:24">
+      <c r="W26" s="45"/>
+      <c r="X26" s="46" t="e">
+        <f>ROUND(X25*X17,2)</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="28" spans="23:24">
+      <c r="W28" s="43" t="s">
+        <v>8</v>
+      </c>
+      <c r="X28" s="44">
+        <f>SUM(X10)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="23:24">
+      <c r="W29" s="45"/>
+      <c r="X29" s="46">
+        <f>ROUND(X28*X17,2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="23:24">
+      <c r="W31" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="X31" s="44" t="e">
+        <f>SUM(#REF!,#REF!,#REF!,#REF!,X4,X5,X9)</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="32" spans="23:24">
+      <c r="W32" s="45"/>
+      <c r="X32" s="46" t="e">
+        <f>ROUND(X31*X17,2)</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="34" spans="23:26">
+      <c r="W34" s="43" t="s">
+        <v>10</v>
+      </c>
+      <c r="X34" s="44" t="e">
+        <f>SUM(#REF!,X6)</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="35" spans="23:26">
+      <c r="W35" s="45"/>
+      <c r="X35" s="46" t="e">
+        <f>ROUND(X34*X17,2)</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="37" spans="23:26">
+      <c r="W37" s="43" t="s">
+        <v>11</v>
+      </c>
+      <c r="X37" s="44">
+        <f>SUM(X11)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="23:26">
+      <c r="W38" s="45"/>
+      <c r="X38" s="46">
+        <f>ROUND(X37*X17,2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="23:26">
+      <c r="W40" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="X16" s="34">
-        <f>(31000*1.05*1.2)+(31000*1.05*1.2*0.35)*1</f>
-        <v>52731</v>
-      </c>
-      <c r="Y16" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" spans="3:30">
-      <c r="C17">
-        <f>C15/C16</f>
-        <v>1.00041431154644</v>
-      </c>
-      <c r="W17" s="35">
-        <v>13</v>
-      </c>
-      <c r="X17" s="34">
-        <v>69300</v>
-      </c>
-      <c r="Y17" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" spans="3:30">
-      <c r="W18" s="35">
-        <v>14</v>
-      </c>
-      <c r="X18" s="34">
-        <v>52731</v>
-      </c>
-      <c r="Y18" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="19" spans="3:30">
-      <c r="W19" s="35">
-        <v>15</v>
-      </c>
-      <c r="X19" s="34">
-        <v>52731</v>
-      </c>
-      <c r="Y19" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="20" spans="3:30">
-      <c r="W20" s="35">
-        <v>16</v>
-      </c>
-      <c r="X20" s="34">
-        <f>(33000*1.05)*2</f>
-        <v>69300</v>
-      </c>
-      <c r="Y20" t="s">
-        <v>31</v>
-      </c>
-      <c r="AB20" s="34">
-        <f>SUM(X53,AB11,AF11)</f>
-        <v>3301168.01</v>
-      </c>
-      <c r="AC20" s="34">
-        <f>SUM(Y53,AC11,AG11)</f>
-        <v>3301168</v>
-      </c>
-      <c r="AD20" s="34">
-        <f>AB20-AC20</f>
-        <v>0.0100000002421439</v>
-      </c>
-    </row>
-    <row r="21" spans="3:30">
-      <c r="W21" s="35">
-        <v>17</v>
-      </c>
-      <c r="X21" s="34">
-        <f>(14450*1.05)</f>
-        <v>15172.5</v>
-      </c>
-      <c r="Y21" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22" spans="3:30">
-      <c r="W22" s="35">
-        <v>18</v>
-      </c>
-      <c r="X22" s="34">
-        <v>15172.5</v>
-      </c>
-      <c r="Y22" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="23" spans="3:30">
-      <c r="W23" s="35">
-        <v>19</v>
-      </c>
-      <c r="X23" s="34">
-        <v>15172.5</v>
-      </c>
-      <c r="Y23" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="24" spans="3:30">
-      <c r="W24" s="35" t="s">
-        <v>20</v>
-      </c>
-      <c r="X24" s="34">
-        <f>SUM(X5:X23)</f>
-        <v>841812.3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:30">
-      <c r="W25" s="47" t="s">
-        <v>40</v>
-      </c>
-      <c r="X25" s="34">
-        <f>X24*5.42</f>
-        <v>4562622.666</v>
-      </c>
-    </row>
-    <row r="26" spans="3:30">
-      <c r="W26" s="48" t="s">
-        <v>32</v>
-      </c>
-      <c r="X26" s="44">
-        <f>X25*0.6</f>
-        <v>2737573.5996</v>
-      </c>
-    </row>
-    <row r="27" spans="3:30">
-      <c r="W27" s="45" t="s">
-        <v>34</v>
-      </c>
-      <c r="X27" s="46">
-        <f>ROUND(X26*C10,2)</f>
-        <v>2819021.13</v>
-      </c>
-    </row>
-    <row r="28" spans="3:30">
-      <c r="W28" s="31"/>
-      <c r="X28" s="32"/>
-    </row>
-    <row r="29" spans="3:30">
-      <c r="O29" t="s">
-        <v>41</v>
-      </c>
-      <c r="W29" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="X29" s="42">
-        <f>5.42*0.6*C10</f>
-        <v>3.34875260722207</v>
-      </c>
-    </row>
-    <row r="31" spans="3:30">
-      <c r="W31" s="49" t="s">
-        <v>12</v>
-      </c>
-      <c r="X31" s="50">
-        <f>SUM(X5,X12,X11)</f>
-        <v>234603.6</v>
-      </c>
-    </row>
-    <row r="32" spans="3:30">
-      <c r="W32" s="51"/>
-      <c r="X32" s="52">
-        <f>ROUND(X31*X29,2)</f>
-        <v>785629.42</v>
-      </c>
-    </row>
-    <row r="34" spans="23:24">
-      <c r="W34" s="49" t="s">
-        <v>16</v>
-      </c>
-      <c r="X34" s="50">
-        <f>SUM(X6,X13)</f>
-        <v>54232.5</v>
-      </c>
-    </row>
-    <row r="35" spans="23:24">
-      <c r="W35" s="51"/>
-      <c r="X35" s="52">
-        <f>ROUND(X34*X29,2)</f>
-        <v>181611.23</v>
-      </c>
-    </row>
-    <row r="37" spans="23:24">
-      <c r="W37" s="49" t="s">
-        <v>31</v>
-      </c>
-      <c r="X37" s="50">
-        <f>SUM(X10,X19,X20)</f>
-        <v>138673.5</v>
-      </c>
-    </row>
-    <row r="38" spans="23:24">
-      <c r="W38" s="51"/>
-      <c r="X38" s="52">
-        <f>ROUND(X37*X29,2)</f>
-        <v>464383.24</v>
-      </c>
-    </row>
-    <row r="40" spans="23:24">
-      <c r="W40" s="49" t="s">
-        <v>38</v>
-      </c>
-      <c r="X40" s="50">
-        <f>SUM(X22)</f>
-        <v>15172.5</v>
-      </c>
-    </row>
-    <row r="41" spans="23:24">
-      <c r="W41" s="51"/>
-      <c r="X41" s="52">
-        <f>ROUND(X40*X29,2)</f>
-        <v>50808.95</v>
-      </c>
-    </row>
-    <row r="43" spans="23:24">
-      <c r="W43" s="49" t="s">
-        <v>19</v>
-      </c>
-      <c r="X43" s="50">
-        <f>SUM(X7,X8,X14,X15,X16,X17,X21)</f>
-        <v>312919.95</v>
-      </c>
-    </row>
-    <row r="44" spans="23:24">
-      <c r="W44" s="51"/>
-      <c r="X44" s="52">
-        <f>ROUND(X43*X29,2)</f>
-        <v>1047891.5</v>
-      </c>
-    </row>
-    <row r="46" spans="23:24">
-      <c r="W46" s="49" t="s">
-        <v>26</v>
-      </c>
-      <c r="X46" s="50">
-        <f>SUM(X9,X18)</f>
-        <v>71037.75</v>
-      </c>
-    </row>
-    <row r="47" spans="23:24">
-      <c r="W47" s="51"/>
-      <c r="X47" s="52">
-        <f>ROUND(X46*X29,2)</f>
-        <v>237887.85</v>
-      </c>
-    </row>
-    <row r="49" spans="23:26">
-      <c r="W49" s="49" t="s">
-        <v>39</v>
-      </c>
-      <c r="X49" s="50">
-        <f>SUM(X23)</f>
-        <v>15172.5</v>
-      </c>
-    </row>
-    <row r="50" spans="23:26">
-      <c r="W50" s="51"/>
-      <c r="X50" s="52">
-        <f>ROUND(X49*X29,2)</f>
-        <v>50808.95</v>
-      </c>
-    </row>
-    <row r="52" spans="23:26">
-      <c r="W52" s="49" t="s">
-        <v>43</v>
-      </c>
-      <c r="X52" s="50">
-        <f>SUM(X31,X34,X37,X40,X43,X46,X49)</f>
-        <v>841812.3</v>
-      </c>
-    </row>
-    <row r="53" spans="23:26">
-      <c r="W53" s="51"/>
-      <c r="X53" s="53">
-        <f>SUM(X32,X35,X38,X41,X44,X47,X50)</f>
-        <v>2819021.14</v>
-      </c>
-      <c r="Y53">
+      <c r="X40" s="44" t="e">
+        <f>SUM(X19,X22,X25,X28,X31,X34,X37)</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="41" spans="23:26">
+      <c r="W41" s="45"/>
+      <c r="X41" s="47" t="e">
+        <f>SUM(X20,X23,X26,X29,X32,X35,X38)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="Y41">
         <v>2819008</v>
       </c>
-      <c r="Z53" s="34">
-        <f>X53-Y53</f>
-        <v>13.1400000001304</v>
+      <c r="Z41" s="34" t="e">
+        <f>X41-Y41</f>
+        <v>#REF!</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="W4:X4"/>
-    <mergeCell ref="AA4:AC4"/>
-    <mergeCell ref="AE4:AG4"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="180" verticalDpi="180"/>
   <headerFooter/>
@@ -2477,7 +1880,7 @@
   <sheetData>
     <row r="1" ht="44.25" customHeight="1" spans="1:7">
       <c r="A1" s="2" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2498,7 +1901,7 @@
     <row r="3" ht="63.75" customHeight="1" spans="1:7">
       <c r="A3" s="3"/>
       <c r="B3" s="5" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
@@ -2509,10 +1912,10 @@
     <row r="4" ht="26.25" customHeight="1" spans="1:7">
       <c r="A4" s="3"/>
       <c r="B4" s="5" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
@@ -2522,7 +1925,7 @@
     <row r="5" ht="18" customHeight="1" spans="1:7">
       <c r="A5" s="3"/>
       <c r="B5" s="5" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
@@ -2537,32 +1940,32 @@
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
-      <c r="G6" s="7">
-        <f>Лист1!C4/D32</f>
-        <v>1.02975172539441</v>
+      <c r="G6" s="7" t="e">
+        <f>Лист1!#REF!/D32</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="7" ht="69.75" customHeight="1" spans="1:7">
       <c r="A7" s="8" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2589,7 +1992,7 @@
     <row r="9" ht="30" customHeight="1" spans="1:7">
       <c r="A9" s="11"/>
       <c r="B9" s="12" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="C9" s="13"/>
       <c r="D9" s="13"/>
@@ -2602,25 +2005,25 @@
         <v>1</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="D10" s="16">
-        <f>ROUND(Лист1!X31*5.42*0.6,2)</f>
-        <v>762930.91</v>
-      </c>
-      <c r="E10" s="16">
+        <f>ROUND(Лист1!X19*5.42*0.6,2)</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="16" t="e">
         <f>ROUND(D10*$G$6,2)</f>
-        <v>785629.42</v>
+        <v>#REF!</v>
       </c>
       <c r="F10" s="16">
         <v>785628</v>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="16" t="e">
         <f>F10-E10</f>
-        <v>-1.42000000004191</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:7">
@@ -2628,25 +2031,25 @@
         <v>2</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="D11" s="16">
-        <f>ROUND(Лист1!X34*5.42*0.6,2)</f>
-        <v>176364.09</v>
-      </c>
-      <c r="E11" s="16">
+        <v>29</v>
+      </c>
+      <c r="D11" s="16" t="e">
+        <f>ROUND(Лист1!X22*5.42*0.6,2)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E11" s="16" t="e">
         <f t="shared" ref="E11:E16" si="0">ROUND(D11*$G$6,2)</f>
-        <v>181611.23</v>
+        <v>#REF!</v>
       </c>
       <c r="F11" s="16">
         <v>181610</v>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="16" t="e">
         <f t="shared" ref="G11:G17" si="1">F11-E11</f>
-        <v>-1.23000000001048</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:7">
@@ -2654,25 +2057,25 @@
         <v>3</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="D12" s="16">
-        <f>ROUND(Лист1!X37*5.42*0.6,2)</f>
-        <v>450966.22</v>
-      </c>
-      <c r="E12" s="16">
+        <v>31</v>
+      </c>
+      <c r="D12" s="16" t="e">
+        <f>ROUND(Лист1!X25*5.42*0.6,2)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E12" s="16" t="e">
         <f t="shared" si="0"/>
-        <v>464383.24</v>
+        <v>#REF!</v>
       </c>
       <c r="F12" s="16">
         <v>464382</v>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="16" t="e">
         <f t="shared" si="1"/>
-        <v>-1.23999999999069</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:7">
@@ -2680,25 +2083,25 @@
         <v>4</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="D13" s="16">
-        <f>ROUND(Лист1!X40*5.42*0.6,2)</f>
-        <v>49340.97</v>
-      </c>
-      <c r="E13" s="16">
+        <f>ROUND(Лист1!X28*5.42*0.6,2)</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="16" t="e">
         <f t="shared" si="0"/>
-        <v>50808.95</v>
+        <v>#REF!</v>
       </c>
       <c r="F13" s="16">
         <v>50805</v>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="16" t="e">
         <f t="shared" si="1"/>
-        <v>-3.94999999999709</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:7">
@@ -2706,25 +2109,25 @@
         <v>5</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="D14" s="16">
-        <f>ROUND(Лист1!X43*5.42*0.6,2)</f>
-        <v>1017615.68</v>
-      </c>
-      <c r="E14" s="16">
+        <v>35</v>
+      </c>
+      <c r="D14" s="16" t="e">
+        <f>ROUND(Лист1!X31*5.42*0.6,2)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E14" s="16" t="e">
         <f t="shared" si="0"/>
-        <v>1047891.5</v>
+        <v>#REF!</v>
       </c>
       <c r="F14" s="16">
         <v>1047890</v>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="16" t="e">
         <f t="shared" si="1"/>
-        <v>-1.5</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:7">
@@ -2732,25 +2135,25 @@
         <v>6</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="D15" s="16">
-        <f>ROUND(Лист1!X46*5.42*0.6,2)</f>
-        <v>231014.76</v>
-      </c>
-      <c r="E15" s="16">
+        <v>37</v>
+      </c>
+      <c r="D15" s="16" t="e">
+        <f>ROUND(Лист1!X34*5.42*0.6,2)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E15" s="16" t="e">
         <f t="shared" si="0"/>
-        <v>237887.85</v>
+        <v>#REF!</v>
       </c>
       <c r="F15" s="16">
         <v>237887</v>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="16" t="e">
         <f t="shared" si="1"/>
-        <v>-0.850000000005821</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:7">
@@ -2758,54 +2161,54 @@
         <v>7</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="D16" s="16">
-        <f>ROUND(Лист1!X49*5.42*0.6,2)</f>
-        <v>49340.97</v>
-      </c>
-      <c r="E16" s="16">
+        <f>ROUND(Лист1!X37*5.42*0.6,2)</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="16" t="e">
         <f t="shared" si="0"/>
-        <v>50808.95</v>
+        <v>#REF!</v>
       </c>
       <c r="F16" s="16">
         <v>50806</v>
       </c>
-      <c r="G16" s="16">
+      <c r="G16" s="16" t="e">
         <f t="shared" si="1"/>
-        <v>-2.94999999999709</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:7">
       <c r="A17" s="11"/>
       <c r="B17" s="17" t="s">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="C17" s="18"/>
-      <c r="D17" s="19">
+      <c r="D17" s="19" t="e">
         <f>SUM(D10:D16)</f>
-        <v>2737573.6</v>
-      </c>
-      <c r="E17" s="19">
+        <v>#REF!</v>
+      </c>
+      <c r="E17" s="19" t="e">
         <f>SUM(E10:E16)</f>
-        <v>2819021.14</v>
+        <v>#REF!</v>
       </c>
       <c r="F17" s="19">
         <f>SUM(F10:F16)</f>
         <v>2819008</v>
       </c>
-      <c r="G17" s="19">
+      <c r="G17" s="19" t="e">
         <f t="shared" si="1"/>
-        <v>-13.1400000001304</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:7">
       <c r="A18" s="11"/>
       <c r="B18" s="12" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="C18" s="13"/>
       <c r="D18" s="13"/>
@@ -2818,22 +2221,22 @@
         <v>8</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="F19" s="16">
         <v>7139</v>
       </c>
       <c r="G19" s="20" t="s">
-        <v>75</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:7">
@@ -2841,10 +2244,10 @@
         <v>9</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="D20" s="21"/>
       <c r="E20" s="21"/>
@@ -2858,10 +2261,10 @@
         <v>10</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="D21" s="21"/>
       <c r="E21" s="21"/>
@@ -2875,10 +2278,10 @@
         <v>11</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D22" s="21"/>
       <c r="E22" s="21"/>
@@ -2892,10 +2295,10 @@
         <v>12</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="D23" s="21"/>
       <c r="E23" s="21"/>
@@ -2909,10 +2312,10 @@
         <v>13</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="D24" s="21"/>
       <c r="E24" s="21"/>
@@ -2926,10 +2329,10 @@
         <v>14</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="D25" s="22"/>
       <c r="E25" s="22"/>
@@ -2941,30 +2344,30 @@
     <row r="26" ht="30" customHeight="1" spans="1:7">
       <c r="A26" s="11"/>
       <c r="B26" s="17" t="s">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="C26" s="18"/>
-      <c r="D26" s="19">
-        <f>ROUND(Лист1!AB10,2)</f>
-        <v>264280.28</v>
-      </c>
-      <c r="E26" s="19">
+      <c r="D26" s="19" t="e">
+        <f>ROUND(Лист1!#REF!,2)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E26" s="19" t="e">
         <f>ROUND(D26*G6,2)</f>
-        <v>272143.07</v>
+        <v>#REF!</v>
       </c>
       <c r="F26" s="19">
         <f>SUM(F19:F25)</f>
         <v>272143</v>
       </c>
-      <c r="G26" s="19">
+      <c r="G26" s="19" t="e">
         <f>F26-E26</f>
-        <v>-0.0700000000069849</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1" spans="1:7">
       <c r="A27" s="11"/>
       <c r="B27" s="12" t="s">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="C27" s="13"/>
       <c r="D27" s="13"/>
@@ -2977,25 +2380,25 @@
         <v>15</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>90</v>
-      </c>
-      <c r="D28" s="16">
-        <f>ROUND(Лист1!AF5*(339.92/62.72)*0.6,2)</f>
-        <v>128807.3</v>
-      </c>
-      <c r="E28" s="16">
+        <v>59</v>
+      </c>
+      <c r="D28" s="16" t="e">
+        <f>ROUND(Лист1!#REF!*(339.92/62.72)*0.6,2)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E28" s="16" t="e">
         <f>ROUND(D28*G6,2)</f>
-        <v>132639.54</v>
+        <v>#REF!</v>
       </c>
       <c r="F28" s="16">
         <v>132654</v>
       </c>
-      <c r="G28" s="16">
+      <c r="G28" s="16" t="e">
         <f>F28-E28</f>
-        <v>14.4599999999919</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1" spans="1:7">
@@ -3003,48 +2406,48 @@
         <v>16</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>92</v>
-      </c>
-      <c r="D29" s="16">
-        <f>ROUND(Лист1!AF6*(339.92/62.72)*0.6,2)</f>
-        <v>75129.03</v>
-      </c>
-      <c r="E29" s="16">
+        <v>61</v>
+      </c>
+      <c r="D29" s="16" t="e">
+        <f>ROUND(Лист1!#REF!*(339.92/62.72)*0.6,2)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E29" s="16" t="e">
         <f>ROUND(D29*G6,2)</f>
-        <v>77364.25</v>
+        <v>#REF!</v>
       </c>
       <c r="F29" s="16">
         <v>77363</v>
       </c>
-      <c r="G29" s="16">
+      <c r="G29" s="16" t="e">
         <f t="shared" ref="G29:G30" si="2">F29-E29</f>
-        <v>-1.25</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1" spans="1:7">
       <c r="A30" s="11"/>
       <c r="B30" s="17" t="s">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="C30" s="18"/>
-      <c r="D30" s="19">
+      <c r="D30" s="19" t="e">
         <f>SUM(D28:D29)</f>
-        <v>203936.33</v>
-      </c>
-      <c r="E30" s="19">
+        <v>#REF!</v>
+      </c>
+      <c r="E30" s="19" t="e">
         <f>SUM(E28:E29)</f>
-        <v>210003.79</v>
+        <v>#REF!</v>
       </c>
       <c r="F30" s="19">
         <f>SUM(F28:F29)</f>
         <v>210017</v>
       </c>
-      <c r="G30" s="19">
+      <c r="G30" s="19" t="e">
         <f t="shared" si="2"/>
-        <v>13.2099999999919</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1" spans="1:7">
@@ -3060,21 +2463,21 @@
       <c r="A32" s="11"/>
       <c r="B32" s="11"/>
       <c r="C32" s="28"/>
-      <c r="D32" s="19">
+      <c r="D32" s="19" t="e">
         <f>SUM(D17,D26,D30)</f>
-        <v>3205790.21</v>
-      </c>
-      <c r="E32" s="19">
+        <v>#REF!</v>
+      </c>
+      <c r="E32" s="19" t="e">
         <f>SUM(E17,E26,E30)</f>
-        <v>3301168</v>
+        <v>#REF!</v>
       </c>
       <c r="F32" s="19">
         <f>SUM(F17,F26,F30)</f>
         <v>3301168</v>
       </c>
-      <c r="G32" s="19">
+      <c r="G32" s="19" t="e">
         <f>SUM(G17,G26,G30)</f>
-        <v>-1.45519152283669e-10</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1" spans="1:7">
